--- a/oven-control-system/02-plc-program/labels/global_labels.xlsx
+++ b/oven-control-system/02-plc-program/labels/global_labels.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4267,12 +4267,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>gSlotElapsed</t>
+          <t>gSlotState</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Double Word [Signed](1..6)</t>
+          <t>Word [Signed](1..6)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4282,25 +4282,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>D4000</t>
+          <t>D70</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LATCH slot 1-6 elapsed seconds</t>
+          <t>slot 1-6 state: 0 empty, 1 curing, 2 complete</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>gCntDoorOpen</t>
+          <t>gSlotElapsed</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Double Word [Signed]</t>
+          <t>Double Word [Signed](1..6)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4310,20 +4310,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>D4020</t>
+          <t>D4000</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>LATCH door opened count</t>
+          <t>LATCH slot 1-6 elapsed seconds</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>gCntDoorClose</t>
+          <t>gCntDoorOpen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4338,20 +4338,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>D4022</t>
+          <t>D4020</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LATCH door closed count</t>
+          <t>LATCH door opened count</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>gCntLotsLoaded</t>
+          <t>gCntDoorClose</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4366,20 +4366,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>D4024</t>
+          <t>D4022</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LATCH lots loaded (slot starts)</t>
+          <t>LATCH door closed count</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>gCntLotsUnloaded</t>
+          <t>gCntLotsLoaded</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4394,20 +4394,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>D4026</t>
+          <t>D4024</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LATCH lots unloaded (normal resets)</t>
+          <t>LATCH lots loaded (slot starts)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>gCntEarlyReset</t>
+          <t>gCntLotsUnloaded</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4422,20 +4422,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>D4028</t>
+          <t>D4026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LATCH early resets by maintenance</t>
+          <t>LATCH lots unloaded (normal resets)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>gTotHtrRunS</t>
+          <t>gCntEarlyReset</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4450,20 +4450,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>D4030</t>
+          <t>D4028</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>LATCH heater running seconds</t>
+          <t>LATCH early resets by maintenance</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>gTotBl1RunS</t>
+          <t>gTotHtrRunS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4478,20 +4478,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>D4032</t>
+          <t>D4030</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LATCH blower 1 running seconds</t>
+          <t>LATCH heater running seconds</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>gTotBl2RunS</t>
+          <t>gTotBl1RunS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4506,25 +4506,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>D4034</t>
+          <t>D4032</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LATCH blower 2 running seconds</t>
+          <t>LATCH blower 1 running seconds</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>gSetHeatUpWdMin</t>
+          <t>gTotBl2RunS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Word [Signed]</t>
+          <t>Double Word [Signed]</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4534,20 +4534,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>D4100</t>
+          <t>D4034</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SET heat-up watchdog, min (10-240)</t>
+          <t>LATCH blower 2 running seconds</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>gSetDoorWdSec</t>
+          <t>gSetHeatUpWdMin</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4562,20 +4562,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>D4101</t>
+          <t>D4100</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SET door watchdog, s (60-1800)</t>
+          <t>SET heat-up watchdog, min (10-240)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>gSetChatterCnt</t>
+          <t>gSetDoorWdSec</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4590,20 +4590,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>D4102</t>
+          <t>D4101</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SET chatter transition count (4-50)</t>
+          <t>SET door watchdog, s (60-1800)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gSetChatterWinS</t>
+          <t>gSetChatterCnt</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4618,20 +4618,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>D4103</t>
+          <t>D4102</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SET chatter window, s (5-60)</t>
+          <t>SET chatter transition count (4-50)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>gSetHtrMinOnS</t>
+          <t>gSetChatterWinS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4646,20 +4646,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>D4104</t>
+          <t>D4103</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SET heater minimum ON, s (5-120)</t>
+          <t>SET chatter window, s (5-60)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>gSetHtrMinOffS</t>
+          <t>gSetHtrMinOnS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4674,20 +4674,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>D4105</t>
+          <t>D4104</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SET heater minimum OFF, s (5-120)</t>
+          <t>SET heater minimum ON, s (5-120)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>gSetManualTmoS</t>
+          <t>gSetHtrMinOffS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4702,20 +4702,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>D4106</t>
+          <t>D4105</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SET manual test auto-exit, s</t>
+          <t>SET heater minimum OFF, s (5-120)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>gSetLoginTmoS</t>
+          <t>gSetManualTmoS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4730,25 +4730,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>D4107</t>
+          <t>D4106</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SET level 2 auto-logout, s</t>
+          <t>SET manual test auto-exit, s</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>gSetSlotTargetS</t>
+          <t>gSetLoginTmoS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Double Word [Signed]</t>
+          <t>Word [Signed]</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4758,25 +4758,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>D4108</t>
+          <t>D4107</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SET slot cure time, s (default 7200)</t>
+          <t>SET level 2 auto-logout, s</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>gSetMaintCode</t>
+          <t>gSetSlotTargetS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Word [Signed]</t>
+          <t>Double Word [Signed]</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4786,20 +4786,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>D4110</t>
+          <t>D4108</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SET MAINTENANCE passcode - change at commissioning</t>
+          <t>SET slot cure time, s (default 7200)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>gSetQualityCode</t>
+          <t>gSetMaintCode</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4814,20 +4814,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>D4111</t>
+          <t>D4110</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SET QUALITY passcode - change at commissioning</t>
+          <t>SET MAINTENANCE passcode - change at commissioning</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>gSetMaxAttempts</t>
+          <t>gSetQualityCode</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4842,20 +4842,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>D4112</t>
+          <t>D4111</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SET failed logins before lockout (default 3)</t>
+          <t>SET QUALITY passcode - change at commissioning</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>gSetLockoutS</t>
+          <t>gSetMaxAttempts</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4870,11 +4870,39 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>D4113</t>
+          <t>D4112</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
+        <is>
+          <t>SET failed logins before lockout (default 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>gSetLockoutS</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Word [Signed]</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VAR_GLOBAL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>D4113</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
         <is>
           <t>SET lockout duration, s (default 300)</t>
         </is>
